--- a/Medios_de_pago.xlsx
+++ b/Medios_de_pago.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1FB8D54-3518-8542-8428-D0A474C95C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65603AF1-5FC5-4A43-995C-E1DB3D1638DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="1000" windowWidth="24460" windowHeight="15520" xr2:uid="{82069770-11EE-1E43-B1F9-C3DF443E8AEF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>MEDIO DE PAGO</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>BALOTO</t>
+  </si>
+  <si>
+    <t>WOMPI</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7834BC7-D9D4-3D48-A859-E4063C8B6372}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" bestFit="1" customWidth="1"/>
@@ -456,6 +459,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
